--- a/task/中间表.xlsx
+++ b/task/中间表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/code/meetchances/solo-coder/sql_transfer/task/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A2DE82-C220-7843-A03A-14C5B8D9A3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FE7417-3C18-0042-9312-9DEE8326B6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="760" windowWidth="28540" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10100" yWindow="2060" windowWidth="28540" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,108 +30,97 @@
     <t>中间表脚本</t>
   </si>
   <si>
-    <t>YWYXJK_KACYZYSX</t>
+    <t>UDWSDIUE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>YSYP_JCS_JC2025Z240016</t>
+    <t>IUEMDNAS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-select to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd') MAN_CHK_TIME_END,A.CHECK_CUSTOMS_CODE,A.I_E_FLAG,A.CHECK_STATE,
---待查时长 ，查验票数
+    <t xml:space="preserve">select to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd') MAN_CHK_TIME_END,A.CHECK_CODE,A.I_E_FLAG,A.CHECK_STATE,
 round(sum( datediff(cy_start_time,A.DISTRIBUTE_TIME,'ss') )/3600,2) dcsx_date ,
 count(distinct A.RECORD_NO) cyps_count,
---查验异常查验时长
 round(sum(case when A.MAN_RESULT_TOTAL='1' then datediff(MAN_CHK_TIME_END,cy_start_time,'ss') /3600 else 0 end ),2) yccysc_date ,
---查验异常票数
 count(distinct case when A.MAN_RESULT_TOTAL='1' then A.RECORD_NO end ) yccyps_count,
 --查验异常4小时完成票数
 count(distinct case when A.MAN_RESULT_TOTAL='1' and datediff(MAN_CHK_TIME_END,cy_start_time,'hh')&lt;4 then A.RECORD_NO end ) cyyc4ps_count,
---取样送检查验时长
 round(sum(case when A.SAMP_INS_RESULT IS NOT NULL then datediff(MAN_CHK_TIME_END,cy_start_time,'ss') /3600 else 0 end ),2) qysjcysc_date ,
---取样送检票数
 count(distinct case when A.SAMP_INS_RESULT IS NOT NULL then A.RECORD_NO end ) qysjps_count,
- --确权查验时长
 round(sum(case when qq_flag='1' then 
 datediff(MAN_CHK_TIME_END,cy_start_time,'ss') /3600 else 0 end ),2) qqcysc_date ,
---确权票数
 count(distinct case when qq_flag='1' then A.RECORD_NO end ) qqps_count,
- --查验正常待查时长
 round(sum(case when A.MAN_RESULT_TOTAL='0' and 
 A.SAMP_INS_RESULT IS NULL and qq_flag='0'
 then datediff(cy_start_time,A.DISTRIBUTE_TIME,'ss') /3600 else 0 end ),2) zcdcsc_date ,
---查验正常票数
 count(distinct case when A.MAN_RESULT_TOTAL='0' and 
 A.SAMP_INS_RESULT IS NULL and qq_flag='0' then A.RECORD_NO end ) cyzcps_count,
- --查验正常查验时长
 round(sum(case when A.MAN_RESULT_TOTAL='0' and 
 A.SAMP_INS_RESULT IS NULL and qq_flag='0'
 then datediff(MAN_CHK_TIME_END,cy_start_time,'ss') /3600 else 0 end ),2) zccysc_date,
---查验正常4小时完成率
 count(distinct case when A.MAN_RESULT_TOTAL='0' and 
 A.SAMP_INS_RESULT IS NULL and qq_flag='0' 
 and datediff(MAN_CHK_TIME_END,cy_start_time,'hh')&lt;4 then A.RECORD_NO end ) zc4ps_count
  from 
  (
- select distinct a.RECORD_NO,a.CHECK_CUSTOMS_CODE,a.MAN_CHK_TIME_END,a.I_E_FLAG,a.CHECK_STATE,a.MAN_RESULT_TOTAL
+ select distinct a.RECORD_NO,a.CHECK_CODE,a.MAN_CHK_TIME_END,a.I_E_FLAG,a.CHECK_STATE,a.MAN_RESULT_TOTAL
  ,a.DISTRIBUTE_TIME,a.SAMP_INS_RESULT,b.MODIFY_TIME cy_start_time,
  --确权标记 1 
- case when A.MAN_CHK_NOTES LIKE '%移送法规确权%'
-AND MAN_CHK_NOTES NOT LIKE '%无需移送法规确权%'
-AND MAN_CHK_NOTES NOT LIKE '%未移送法规确权%'
-AND MAN_CHK_NOTES NOT LIKE '%不移送法规确权%'
-AND MAN_CHK_NOTES NOT LIKE '%不作移送法规确权%'
-AND MAN_CHK_NOTES NOT LIKE '%不做移送法规确权%'
-AND MAN_CHK_NOTES NOT LIKE '%无法移送法规确权%' then 1 else 0 end qq_flag 
+ case when A.MAN_CHK_NOTES LIKE '%移送%'
+AND MAN_CHK_NOTES NOT LIKE '%无需移送%'
+AND MAN_CHK_NOTES NOT LIKE '%未移送%'
+AND MAN_CHK_NOTES NOT LIKE '%不移送%'
+AND MAN_CHK_NOTES NOT LIKE '%不作移送%'
+AND MAN_CHK_NOTES NOT LIKE '%不做移送%'
+AND MAN_CHK_NOTES NOT LIKE '%无法移送%' then 1 else 0 end qq_flag 
  from 
 base_data.pub_rsk4_ci_check_man_work_head a left join (
 select EXCUTE_TASK_RECORD_NO,min(MODIFY_TIME) MODIFY_TIME from base_data.pub_rsk4_ci_workflow_excute_content 
 where EXCUTE_TASK_CODE='4' 
 group by EXCUTE_TASK_RECORD_NO) b on B.EXCUTE_TASK_RECORD_NO=A.RECORD_NO
-where A.WF_STATUS='6' --AND A.CHECK_CUSTOMS_CODE LIKE '53%' 
+where A.WF_STATUS='6' --AND A.CHECK_CODE LIKE '53%' 
 AND to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd')&gt;=substr(dateadd(getdate(),-23,'MM'),1,7)||'-01' 
  ) a
-group by to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd'),A.CHECK_CUSTOMS_CODE,A.I_E_FLAG,A.CHECK_STATE
-</t>
+group by to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd'),A.CHECK_CODE,A.I_E_FLAG,A.CHECK_STATE
+ </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-SELECT b.CUSTOMS_CODE
+    <t xml:space="preserve">SELECT b.CODE
  ,TO_CHAR(a.create_time,'yyyymmdd') AS D_DATE
  ,(
- CASE WHEN a.QUA = 'A1201' THEN '跨境电子商务电商企业'
- WHEN a.QUA = 'A1202' THEN '境外跨境电商企业的境内代理人'
- WHEN a.QUA = 'A1211' THEN '跨境电子商务平台企业'
- WHEN a.QUA = 'A1231' THEN '跨境电子商务物流企业'
- WHEN a.QUA = 'A1232' THEN '跨境电子商务物流企业(仅B2B)'
- WHEN a.QUA = 'A1241' THEN '跨境电子商务支付企业'
- WHEN a.QUA = 'A1251' THEN '跨境电子商务监管场所运营人'
+ CASE WHEN a.QUA = 'D0001' THEN '跨境电商'
+ WHEN a.QUA = 'D0002' THEN '跨境电商的境内代理人'
+ WHEN a.QUA = 'D0011' THEN '跨境电商平台企业'
+ WHEN a.QUA = 'D0031' THEN '跨境电商物流企业'
+ WHEN a.QUA = 'D0032' THEN '跨境电商物流企业(仅B2B)'
+ WHEN a.QUA = 'D0041' THEN '跨境电商支付企业'
+ WHEN a.QUA = 'D0051' THEN '跨境电商监管场所运营人'
  END
  ) AS QUA
  ,COUNT(DISTINCT a.social_credit_code) AS ETPS_COUNT
- ,CusCodeCname(b.CUSTOMS_CODE) as customs_name
- ,CusCodeCname(substr(b.CUSTOMS_CODE,1,2)) as customsname
+ ,CusCodeCname(b.CODE) as name
+ ,CusCodeCname(substr(b.CODE,1,2)) as customsname
  ,to_char(now(),'yyyy-mm-dd hh:mi:ss') time_t
 FROM base_data.pub_xz3_ent_qualification a
 , base_data.pub_xz3_ent_company b
 WHERE a.ETPS_NO = b.ETPS_NO
-AND a.QUA IN ('A1201','A1202','A1211','A1231','A1232','A1241','A1251')
+AND a.QUA IN ('D0001','D0002','D0011','D0031','D0032','D0041','D0051')
 AND a.SIGNOUT_FLAG = '0'
-GROUP BY b.CUSTOMS_CODE
+GROUP BY b.CODE
  ,TO_CHAR(a.create_time,'yyyymmdd')
  ,(
- CASE WHEN a.QUA = 'A1201' THEN '跨境电子商务电商企业'
- WHEN a.QUA = 'A1202' THEN '境外跨境电商企业的境内代理人'
- WHEN a.QUA = 'A1211' THEN '跨境电子商务平台企业'
- WHEN a.QUA = 'A1231' THEN '跨境电子商务物流企业'
- WHEN a.QUA = 'A1232' THEN '跨境电子商务物流企业(仅B2B)'
- WHEN a.QUA = 'A1241' THEN '跨境电子商务支付企业'
- WHEN a.QUA = 'A1251' THEN '跨境电子商务监管场所运营人'
+ CASE WHEN a.QUA = 'D0001' THEN '跨境电商'
+ WHEN a.QUA = 'D0002' THEN '跨境电商的境内代理人'
+ WHEN a.QUA = 'D0011' THEN '跨境电商平台企业'
+ WHEN a.QUA = 'D0031' THEN '跨境电商物流企业'
+ WHEN a.QUA = 'D0032' THEN '跨境电商物流企业(仅B2B)'
+ WHEN a.QUA = 'D0041' THEN '跨境电商支付企业'
+ WHEN a.QUA = 'D0051' THEN '跨境电商监管场所运营人'
  END
  )
 ;
-</t>
+ </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -200,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,6 +198,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,7 +520,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="19" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -536,7 +528,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="19" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">

--- a/task/中间表.xlsx
+++ b/task/中间表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/code/meetchances/solo-coder/sql_transfer/task/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FE7417-3C18-0042-9312-9DEE8326B6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1723BA57-AAED-7F44-85C4-941504AF9C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10100" yWindow="2060" windowWidth="28540" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,12 +38,49 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">SELECT b.CODE
+ ,TO_CHAR(a.create_time,'yyyymmdd') AS D_DATE
+ ,(
+ CASE WHEN a.QUA = 'D0001' THEN '跨境电商'
+ WHEN a.QUA = 'D0002' THEN '跨境电商的境内代理人'
+ WHEN a.QUA = 'D0011' THEN '跨境电商平台企业'
+ WHEN a.QUA = 'D0031' THEN '跨境电商物流企业'
+ WHEN a.QUA = 'D0032' THEN '跨境电商物流企业(仅B2B)'
+ WHEN a.QUA = 'D0041' THEN '跨境电商支付企业'
+ WHEN a.QUA = 'D0051' THEN '跨境电商监管场所运营人'
+ END
+ ) AS QUA
+ ,COUNT(DISTINCT a.social_credit_code) AS ETPS_COUNT
+ ,CusCodeCname(b.CODE) as name
+ ,CusCodeCname(substr(b.CODE,1,2)) as customsname
+ ,to_char(now(),'yyyy-mm-dd hh:mi:ss') time_t
+FROM base_data.pub_xz3_ent_qualification a
+, base_data.pub_xz3_ent_company b
+WHERE a.ETPS_NO = b.ETPS_NO
+AND a.QUA IN ('D0001','D0002','D0011','D0031','D0032','D0041','D0051')
+AND a.SIGNOUT_FLAG = '0'
+GROUP BY b.CODE
+ ,TO_CHAR(a.create_time,'yyyymmdd')
+ ,(
+ CASE WHEN a.QUA = 'D0001' THEN '跨境电商'
+ WHEN a.QUA = 'D0002' THEN '跨境电商的境内代理人'
+ WHEN a.QUA = 'D0011' THEN '跨境电商平台企业'
+ WHEN a.QUA = 'D0031' THEN '跨境电商物流企业'
+ WHEN a.QUA = 'D0032' THEN '跨境电商物流企业(仅B2B)'
+ WHEN a.QUA = 'D0041' THEN '跨境电商支付企业'
+ WHEN a.QUA = 'D0051' THEN '跨境电商监管场所运营人'
+ END
+ )
+;
+ </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">select to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd') MAN_CHK_TIME_END,A.CHECK_CODE,A.I_E_FLAG,A.CHECK_STATE,
 round(sum( datediff(cy_start_time,A.DISTRIBUTE_TIME,'ss') )/3600,2) dcsx_date ,
 count(distinct A.RECORD_NO) cyps_count,
 round(sum(case when A.MAN_RESULT_TOTAL='1' then datediff(MAN_CHK_TIME_END,cy_start_time,'ss') /3600 else 0 end ),2) yccysc_date ,
 count(distinct case when A.MAN_RESULT_TOTAL='1' then A.RECORD_NO end ) yccyps_count,
---查验异常4小时完成票数
 count(distinct case when A.MAN_RESULT_TOTAL='1' and datediff(MAN_CHK_TIME_END,cy_start_time,'hh')&lt;4 then A.RECORD_NO end ) cyyc4ps_count,
 round(sum(case when A.SAMP_INS_RESULT IS NOT NULL then datediff(MAN_CHK_TIME_END,cy_start_time,'ss') /3600 else 0 end ),2) qysjcysc_date ,
 count(distinct case when A.SAMP_INS_RESULT IS NOT NULL then A.RECORD_NO end ) qysjps_count,
@@ -82,44 +119,6 @@
 AND to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd')&gt;=substr(dateadd(getdate(),-23,'MM'),1,7)||'-01' 
  ) a
 group by to_char(A.MAN_CHK_TIME_END,'yyyy-mm-dd'),A.CHECK_CODE,A.I_E_FLAG,A.CHECK_STATE
- </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT b.CODE
- ,TO_CHAR(a.create_time,'yyyymmdd') AS D_DATE
- ,(
- CASE WHEN a.QUA = 'D0001' THEN '跨境电商'
- WHEN a.QUA = 'D0002' THEN '跨境电商的境内代理人'
- WHEN a.QUA = 'D0011' THEN '跨境电商平台企业'
- WHEN a.QUA = 'D0031' THEN '跨境电商物流企业'
- WHEN a.QUA = 'D0032' THEN '跨境电商物流企业(仅B2B)'
- WHEN a.QUA = 'D0041' THEN '跨境电商支付企业'
- WHEN a.QUA = 'D0051' THEN '跨境电商监管场所运营人'
- END
- ) AS QUA
- ,COUNT(DISTINCT a.social_credit_code) AS ETPS_COUNT
- ,CusCodeCname(b.CODE) as name
- ,CusCodeCname(substr(b.CODE,1,2)) as customsname
- ,to_char(now(),'yyyy-mm-dd hh:mi:ss') time_t
-FROM base_data.pub_xz3_ent_qualification a
-, base_data.pub_xz3_ent_company b
-WHERE a.ETPS_NO = b.ETPS_NO
-AND a.QUA IN ('D0001','D0002','D0011','D0031','D0032','D0041','D0051')
-AND a.SIGNOUT_FLAG = '0'
-GROUP BY b.CODE
- ,TO_CHAR(a.create_time,'yyyymmdd')
- ,(
- CASE WHEN a.QUA = 'D0001' THEN '跨境电商'
- WHEN a.QUA = 'D0002' THEN '跨境电商的境内代理人'
- WHEN a.QUA = 'D0011' THEN '跨境电商平台企业'
- WHEN a.QUA = 'D0031' THEN '跨境电商物流企业'
- WHEN a.QUA = 'D0032' THEN '跨境电商物流企业(仅B2B)'
- WHEN a.QUA = 'D0041' THEN '跨境电商支付企业'
- WHEN a.QUA = 'D0051' THEN '跨境电商监管场所运营人'
- END
- )
-;
  </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -524,7 +523,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="19" customHeight="1">
@@ -532,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
